--- a/output/Data and Chart Outputs/philippines_dam_levels.xlsx
+++ b/output/Data and Chart Outputs/philippines_dam_levels.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Units" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Water year - Angat" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Water year - San Roque" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Water year - Magat" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Water year - Pantabangan" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Limits" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Units" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Water year - Angat" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Water year - San Roque" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Water year - Magat" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Water year - Pantabangan" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Daily" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Limits" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -145,18 +145,18 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Angat dam water level (Metro Manila water supply and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-03</a:t>
+              <a:t>Angat dam water level (Metro Manila water supply and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-04</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -173,8 +173,8 @@
             <v> </v>
           </tx>
           <spPr>
-            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:noFill/>
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -197,10 +197,10 @@
             <v>5-year range (2021/22-2025/26)</v>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="AFC6D9"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -230,7 +230,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+            <a:ln w="19050">
               <a:solidFill>
                 <a:srgbClr val="6E6E6E"/>
               </a:solidFill>
@@ -240,7 +240,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -266,7 +266,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+            <a:ln w="19050">
               <a:solidFill>
                 <a:srgbClr val="EB6834"/>
               </a:solidFill>
@@ -276,7 +276,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -302,7 +302,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="38100">
+            <a:ln w="38100">
               <a:solidFill>
                 <a:srgbClr val="0B3A66"/>
               </a:solidFill>
@@ -312,7 +312,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -343,8 +343,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-2700000" vert="horz"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -372,8 +372,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -389,10 +389,10 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
-        <majorUnit val="0.01"/>
+        <majorUnit val="0.025"/>
       </valAx>
       <spPr>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -406,7 +406,7 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -415,18 +415,18 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>San Roque dam water level (hydro, Agno river; PAGASA) - water year (Oct-Sep), data to 2026-10-03</a:t>
+              <a:t>San Roque dam water level (hydro, Agno river; PAGASA) - water year (Oct-Sep), data to 2026-10-04</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -443,8 +443,8 @@
             <v> </v>
           </tx>
           <spPr>
-            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:noFill/>
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -467,10 +467,10 @@
             <v>5-year range (2021/22-2025/26)</v>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="AFC6D9"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -500,7 +500,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+            <a:ln w="19050">
               <a:solidFill>
                 <a:srgbClr val="6E6E6E"/>
               </a:solidFill>
@@ -510,7 +510,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -536,7 +536,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+            <a:ln w="19050">
               <a:solidFill>
                 <a:srgbClr val="EB6834"/>
               </a:solidFill>
@@ -546,7 +546,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -572,7 +572,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="38100">
+            <a:ln w="38100">
               <a:solidFill>
                 <a:srgbClr val="0B3A66"/>
               </a:solidFill>
@@ -582,7 +582,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -613,8 +613,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-2700000" vert="horz"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -633,7 +633,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="283"/>
+          <max val="284"/>
           <min val="282"/>
         </scaling>
         <delete val="0"/>
@@ -642,8 +642,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -659,10 +659,10 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
-        <majorUnit val="0.1"/>
+        <majorUnit val="0.2"/>
       </valAx>
       <spPr>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -676,7 +676,7 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -685,18 +685,18 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Magat dam water level (irrigation and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-03</a:t>
+              <a:t>Magat dam water level (irrigation and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-04</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -713,8 +713,8 @@
             <v> </v>
           </tx>
           <spPr>
-            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:noFill/>
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -737,10 +737,10 @@
             <v>5-year range (2021/22-2025/26)</v>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="AFC6D9"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -770,7 +770,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+            <a:ln w="19050">
               <a:solidFill>
                 <a:srgbClr val="6E6E6E"/>
               </a:solidFill>
@@ -780,7 +780,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -806,7 +806,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+            <a:ln w="19050">
               <a:solidFill>
                 <a:srgbClr val="EB6834"/>
               </a:solidFill>
@@ -816,7 +816,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -842,7 +842,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="38100">
+            <a:ln w="38100">
               <a:solidFill>
                 <a:srgbClr val="0B3A66"/>
               </a:solidFill>
@@ -852,7 +852,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -883,8 +883,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-2700000" vert="horz"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -912,8 +912,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -932,7 +932,7 @@
         <majorUnit val="0.2"/>
       </valAx>
       <spPr>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -946,7 +946,7 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -955,18 +955,18 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Pantabangan dam water level (irrigation and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-03</a:t>
+              <a:t>Pantabangan dam water level (irrigation and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-04</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -983,8 +983,8 @@
             <v> </v>
           </tx>
           <spPr>
-            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:noFill/>
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1007,10 +1007,10 @@
             <v>5-year range (2021/22-2025/26)</v>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="AFC6D9"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1040,7 +1040,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+            <a:ln w="19050">
               <a:solidFill>
                 <a:srgbClr val="6E6E6E"/>
               </a:solidFill>
@@ -1050,7 +1050,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1076,7 +1076,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+            <a:ln w="19050">
               <a:solidFill>
                 <a:srgbClr val="EB6834"/>
               </a:solidFill>
@@ -1086,7 +1086,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1112,7 +1112,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="38100">
+            <a:ln w="38100">
               <a:solidFill>
                 <a:srgbClr val="0B3A66"/>
               </a:solidFill>
@@ -1122,7 +1122,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1153,8 +1153,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-2700000" vert="horz"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1182,8 +1182,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1202,7 +1202,7 @@
         <majorUnit val="0.05"/>
       </valAx>
       <spPr>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -1216,7 +1216,7 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -1225,7 +1225,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>8</col>
@@ -1240,9 +1240,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1252,7 +1252,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>8</col>
@@ -1267,9 +1267,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1279,7 +1279,7 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>8</col>
@@ -1294,9 +1294,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1306,7 +1306,7 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>8</col>
@@ -1321,9 +1321,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1659,7 +1659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Daily from 2026-10-02 to 2026-10-03 - PAGASA posts only today's and yesterday's readings, so the history here starts with this pull's first run. Luzon reservoirs: Angat (Metro Manila water supply, 218 MW hydro), Ipo and La Mesa (water supply), Ambuklao, Binga, San Roque (hydro, Agno river), Pantabangan and Magat (irrigation + hydro), Caliraya (pumped storage).</t>
+          <t>Daily from 2026-10-02 to 2026-10-04 - PAGASA posts only today's and yesterday's readings, so the history here starts with this pull's first run. Luzon reservoirs: Angat (Metro Manila water supply, 218 MW hydro), Ipo and La Mesa (water supply), Ambuklao, Binga, San Roque (hydro, Agno river), Pantabangan and Magat (irrigation + hydro), Caliraya (pumped storage).</t>
         </is>
       </c>
     </row>
@@ -1780,6 +1780,9 @@
         <is>
           <t>04-Oct</t>
         </is>
+      </c>
+      <c r="G5" t="n">
+        <v>208.39</v>
       </c>
     </row>
     <row r="6">
@@ -4468,6 +4471,9 @@
           <t>04-Oct</t>
         </is>
       </c>
+      <c r="G5" t="n">
+        <v>283.22</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7155,6 +7161,9 @@
           <t>04-Oct</t>
         </is>
       </c>
+      <c r="G5" t="n">
+        <v>190.38</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -9842,6 +9851,9 @@
           <t>04-Oct</t>
         </is>
       </c>
+      <c r="G5" t="n">
+        <v>208.26</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -12437,7 +12449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12554,6 +12566,38 @@
       </c>
       <c r="J3" t="n">
         <v>286.36</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B4" t="n">
+        <v>208.39</v>
+      </c>
+      <c r="C4" t="n">
+        <v>100.18</v>
+      </c>
+      <c r="D4" t="n">
+        <v>79.16</v>
+      </c>
+      <c r="E4" t="n">
+        <v>750.95</v>
+      </c>
+      <c r="F4" t="n">
+        <v>574.34</v>
+      </c>
+      <c r="G4" t="n">
+        <v>283.22</v>
+      </c>
+      <c r="H4" t="n">
+        <v>208.26</v>
+      </c>
+      <c r="I4" t="n">
+        <v>190.38</v>
+      </c>
+      <c r="J4" t="n">
+        <v>286.48</v>
       </c>
     </row>
   </sheetData>
@@ -12602,11 +12646,11 @@
         <v>210</v>
       </c>
       <c r="C2" t="n">
-        <v>186.91</v>
+        <v>187.28</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -12624,7 +12668,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -12642,7 +12686,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -12660,7 +12704,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -12678,7 +12722,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -12692,11 +12736,11 @@
         <v>280</v>
       </c>
       <c r="C7" t="n">
-        <v>269.8</v>
+        <v>270.15</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -12710,11 +12754,11 @@
         <v>218.5</v>
       </c>
       <c r="C8" t="n">
-        <v>216.34</v>
+        <v>216.43</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -12728,11 +12772,11 @@
         <v>193</v>
       </c>
       <c r="C9" t="n">
-        <v>186.21</v>
+        <v>186.29</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -12750,7 +12794,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>

--- a/output/Data and Chart Outputs/philippines_dam_levels.xlsx
+++ b/output/Data and Chart Outputs/philippines_dam_levels.xlsx
@@ -1644,7 +1644,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Daily: reservoir water level at 08:00, metres above mean sea level, one column per dam. Limits: normal high water level (NHWL, full) and the day's rule-curve elevation (the operating guide level) from the latest run.</t>
+          <t>Daily: reservoir water level at 08:00, metres above mean sea level, one column per dam. Limits: normal high water level (NHWL, full) and the day's rule-curve elevation (the operating guide level) from the latest run; blank where PAGASA publishes none (it prints 0: Caliraya's NHWL and rule curve, Ipo and La Mesa's rule curve).</t>
         </is>
       </c>
     </row>
@@ -12663,9 +12663,6 @@
       <c r="B3" t="n">
         <v>101.1</v>
       </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>2026-10-04</t>
@@ -12681,9 +12678,6 @@
       <c r="B4" t="n">
         <v>80.15000000000001</v>
       </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>2026-10-04</t>
@@ -12785,12 +12779,6 @@
         <is>
           <t>Caliraya</t>
         </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/output/Data and Chart Outputs/philippines_dam_levels.xlsx
+++ b/output/Data and Chart Outputs/philippines_dam_levels.xlsx
@@ -156,7 +156,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Angat dam water level (Metro Manila water supply and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-04</a:t>
+              <a:t>Angat dam water level (Metro Manila water supply and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-05</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -389,7 +389,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
-        <majorUnit val="0.025"/>
+        <majorUnit val="0.05"/>
       </valAx>
       <spPr>
         <a:ln>
@@ -426,7 +426,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>San Roque dam water level (hydro, Agno river; PAGASA) - water year (Oct-Sep), data to 2026-10-04</a:t>
+              <a:t>San Roque dam water level (hydro, Agno river; PAGASA) - water year (Oct-Sep), data to 2026-10-05</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -696,7 +696,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Magat dam water level (irrigation and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-04</a:t>
+              <a:t>Magat dam water level (irrigation and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-05</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -966,7 +966,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Pantabangan dam water level (irrigation and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-04</a:t>
+              <a:t>Pantabangan dam water level (irrigation and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-05</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1199,7 +1199,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
-        <majorUnit val="0.05"/>
+        <majorUnit val="0.1"/>
       </valAx>
       <spPr>
         <a:ln>
@@ -1659,7 +1659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Daily from 2026-10-02 to 2026-10-04 - PAGASA posts only today's and yesterday's readings, so the history here starts with this pull's first run. Luzon reservoirs: Angat (Metro Manila water supply, 218 MW hydro), Ipo and La Mesa (water supply), Ambuklao, Binga, San Roque (hydro, Agno river), Pantabangan and Magat (irrigation + hydro), Caliraya (pumped storage).</t>
+          <t>Daily from 2026-10-02 to 2026-10-05 - PAGASA posts only today's and yesterday's readings, so the history here starts with this pull's first run. Luzon reservoirs: Angat (Metro Manila water supply, 218 MW hydro), Ipo and La Mesa (water supply), Ambuklao, Binga, San Roque (hydro, Agno river), Pantabangan and Magat (irrigation + hydro), Caliraya (pumped storage).</t>
         </is>
       </c>
     </row>
@@ -1790,6 +1790,9 @@
         <is>
           <t>05-Oct</t>
         </is>
+      </c>
+      <c r="G6" t="n">
+        <v>208.24</v>
       </c>
     </row>
     <row r="7">
@@ -4481,6 +4484,9 @@
           <t>05-Oct</t>
         </is>
       </c>
+      <c r="G6" t="n">
+        <v>283.05</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7171,6 +7177,9 @@
           <t>05-Oct</t>
         </is>
       </c>
+      <c r="G6" t="n">
+        <v>190.35</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9861,6 +9870,9 @@
           <t>05-Oct</t>
         </is>
       </c>
+      <c r="G6" t="n">
+        <v>208.37</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -12449,7 +12461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12598,6 +12610,38 @@
       </c>
       <c r="J4" t="n">
         <v>286.48</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B5" t="n">
+        <v>208.24</v>
+      </c>
+      <c r="C5" t="n">
+        <v>100.15</v>
+      </c>
+      <c r="D5" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>751.29</v>
+      </c>
+      <c r="F5" t="n">
+        <v>573.47</v>
+      </c>
+      <c r="G5" t="n">
+        <v>283.05</v>
+      </c>
+      <c r="H5" t="n">
+        <v>208.37</v>
+      </c>
+      <c r="I5" t="n">
+        <v>190.35</v>
+      </c>
+      <c r="J5" t="n">
+        <v>286.87</v>
       </c>
     </row>
   </sheetData>
@@ -12646,11 +12690,11 @@
         <v>210</v>
       </c>
       <c r="C2" t="n">
-        <v>187.28</v>
+        <v>187.65</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -12665,7 +12709,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -12680,7 +12724,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -12698,7 +12742,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -12716,7 +12760,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -12730,11 +12774,11 @@
         <v>280</v>
       </c>
       <c r="C7" t="n">
-        <v>270.15</v>
+        <v>270.51</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -12748,11 +12792,11 @@
         <v>218.5</v>
       </c>
       <c r="C8" t="n">
-        <v>216.43</v>
+        <v>216.51</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -12766,11 +12810,11 @@
         <v>193</v>
       </c>
       <c r="C9" t="n">
-        <v>186.29</v>
+        <v>186.36</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -12782,7 +12826,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>

--- a/output/Data and Chart Outputs/philippines_dam_levels.xlsx
+++ b/output/Data and Chart Outputs/philippines_dam_levels.xlsx
@@ -156,7 +156,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Angat dam water level (Metro Manila water supply and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-05</a:t>
+              <a:t>Angat dam water level (Metro Manila water supply and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-06</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -389,7 +389,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
-        <majorUnit val="0.05"/>
+        <majorUnit val="0.1"/>
       </valAx>
       <spPr>
         <a:ln>
@@ -426,7 +426,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>San Roque dam water level (hydro, Agno river; PAGASA) - water year (Oct-Sep), data to 2026-10-05</a:t>
+              <a:t>San Roque dam water level (hydro, Agno river; PAGASA) - water year (Oct-Sep), data to 2026-10-06</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -696,7 +696,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Magat dam water level (irrigation and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-05</a:t>
+              <a:t>Magat dam water level (irrigation and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-06</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -966,7 +966,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Pantabangan dam water level (irrigation and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-05</a:t>
+              <a:t>Pantabangan dam water level (irrigation and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-06</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1659,7 +1659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Daily from 2026-10-02 to 2026-10-05 - PAGASA posts only today's and yesterday's readings, so the history here starts with this pull's first run. Luzon reservoirs: Angat (Metro Manila water supply, 218 MW hydro), Ipo and La Mesa (water supply), Ambuklao, Binga, San Roque (hydro, Agno river), Pantabangan and Magat (irrigation + hydro), Caliraya (pumped storage).</t>
+          <t>Daily from 2026-10-02 to 2026-10-06 - PAGASA posts only today's and yesterday's readings, so the history here starts with this pull's first run. Luzon reservoirs: Angat (Metro Manila water supply, 218 MW hydro), Ipo and La Mesa (water supply), Ambuklao, Binga, San Roque (hydro, Agno river), Pantabangan and Magat (irrigation + hydro), Caliraya (pumped storage).</t>
         </is>
       </c>
     </row>
@@ -1800,6 +1800,9 @@
         <is>
           <t>06-Oct</t>
         </is>
+      </c>
+      <c r="G7" t="n">
+        <v>208.07</v>
       </c>
     </row>
     <row r="8">
@@ -4494,6 +4497,9 @@
           <t>06-Oct</t>
         </is>
       </c>
+      <c r="G7" t="n">
+        <v>282.96</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7187,6 +7193,9 @@
           <t>06-Oct</t>
         </is>
       </c>
+      <c r="G7" t="n">
+        <v>190.71</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9880,6 +9889,9 @@
           <t>06-Oct</t>
         </is>
       </c>
+      <c r="G7" t="n">
+        <v>208.53</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -12461,7 +12473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12642,6 +12654,38 @@
       </c>
       <c r="J5" t="n">
         <v>286.87</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B6" t="n">
+        <v>208.07</v>
+      </c>
+      <c r="C6" t="n">
+        <v>99.98</v>
+      </c>
+      <c r="D6" t="n">
+        <v>79.26000000000001</v>
+      </c>
+      <c r="E6" t="n">
+        <v>751.53</v>
+      </c>
+      <c r="F6" t="n">
+        <v>573.8</v>
+      </c>
+      <c r="G6" t="n">
+        <v>282.96</v>
+      </c>
+      <c r="H6" t="n">
+        <v>208.53</v>
+      </c>
+      <c r="I6" t="n">
+        <v>190.71</v>
+      </c>
+      <c r="J6" t="n">
+        <v>286.58</v>
       </c>
     </row>
   </sheetData>
@@ -12690,11 +12734,11 @@
         <v>210</v>
       </c>
       <c r="C2" t="n">
-        <v>187.65</v>
+        <v>188.03</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
     </row>
@@ -12709,7 +12753,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
     </row>
@@ -12724,7 +12768,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
     </row>
@@ -12742,7 +12786,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
     </row>
@@ -12760,7 +12804,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
     </row>
@@ -12774,11 +12818,11 @@
         <v>280</v>
       </c>
       <c r="C7" t="n">
-        <v>270.51</v>
+        <v>270.86</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
     </row>
@@ -12792,11 +12836,11 @@
         <v>218.5</v>
       </c>
       <c r="C8" t="n">
-        <v>216.51</v>
+        <v>216.6</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
     </row>
@@ -12810,11 +12854,11 @@
         <v>193</v>
       </c>
       <c r="C9" t="n">
-        <v>186.36</v>
+        <v>186.43</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
     </row>
@@ -12826,7 +12870,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
     </row>

--- a/output/Data and Chart Outputs/philippines_dam_levels.xlsx
+++ b/output/Data and Chart Outputs/philippines_dam_levels.xlsx
@@ -156,7 +156,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Angat dam water level (Metro Manila water supply and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-06</a:t>
+              <a:t>Angat dam water level (Metro Manila water supply and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-07</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -364,7 +364,7 @@
         <scaling>
           <orientation val="minMax"/>
           <max val="209"/>
-          <min val="208"/>
+          <min val="207"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -426,7 +426,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>San Roque dam water level (hydro, Agno river; PAGASA) - water year (Oct-Sep), data to 2026-10-06</a:t>
+              <a:t>San Roque dam water level (hydro, Agno river; PAGASA) - water year (Oct-Sep), data to 2026-10-07</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -696,7 +696,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Magat dam water level (irrigation and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-06</a:t>
+              <a:t>Magat dam water level (irrigation and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-07</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -903,7 +903,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="191"/>
+          <max val="192"/>
           <min val="189"/>
         </scaling>
         <delete val="0"/>
@@ -929,7 +929,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
-        <majorUnit val="0.2"/>
+        <majorUnit val="0.5"/>
       </valAx>
       <spPr>
         <a:ln>
@@ -966,7 +966,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Pantabangan dam water level (irrigation and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-06</a:t>
+              <a:t>Pantabangan dam water level (irrigation and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-07</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1199,7 +1199,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
-        <majorUnit val="0.1"/>
+        <majorUnit val="0.2"/>
       </valAx>
       <spPr>
         <a:ln>
@@ -1659,7 +1659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Daily from 2026-10-02 to 2026-10-06 - PAGASA posts only today's and yesterday's readings, so the history here starts with this pull's first run. Luzon reservoirs: Angat (Metro Manila water supply, 218 MW hydro), Ipo and La Mesa (water supply), Ambuklao, Binga, San Roque (hydro, Agno river), Pantabangan and Magat (irrigation + hydro), Caliraya (pumped storage).</t>
+          <t>Daily from 2026-10-02 to 2026-10-07 - PAGASA posts only today's and yesterday's readings, so the history here starts with this pull's first run. Luzon reservoirs: Angat (Metro Manila water supply, 218 MW hydro), Ipo and La Mesa (water supply), Ambuklao, Binga, San Roque (hydro, Agno river), Pantabangan and Magat (irrigation + hydro), Caliraya (pumped storage).</t>
         </is>
       </c>
     </row>
@@ -1810,6 +1810,9 @@
         <is>
           <t>07-Oct</t>
         </is>
+      </c>
+      <c r="G8" t="n">
+        <v>207.95</v>
       </c>
     </row>
     <row r="9">
@@ -4507,6 +4510,9 @@
           <t>07-Oct</t>
         </is>
       </c>
+      <c r="G8" t="n">
+        <v>283.15</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7203,6 +7209,9 @@
           <t>07-Oct</t>
         </is>
       </c>
+      <c r="G8" t="n">
+        <v>191.13</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -9899,6 +9908,9 @@
           <t>07-Oct</t>
         </is>
       </c>
+      <c r="G8" t="n">
+        <v>208.68</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -12473,7 +12485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12686,6 +12698,38 @@
       </c>
       <c r="J6" t="n">
         <v>286.58</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B7" t="n">
+        <v>207.95</v>
+      </c>
+      <c r="C7" t="n">
+        <v>100.33</v>
+      </c>
+      <c r="D7" t="n">
+        <v>79.34999999999999</v>
+      </c>
+      <c r="E7" t="n">
+        <v>751.5599999999999</v>
+      </c>
+      <c r="F7" t="n">
+        <v>574.04</v>
+      </c>
+      <c r="G7" t="n">
+        <v>283.15</v>
+      </c>
+      <c r="H7" t="n">
+        <v>208.68</v>
+      </c>
+      <c r="I7" t="n">
+        <v>191.13</v>
+      </c>
+      <c r="J7" t="n">
+        <v>286.28</v>
       </c>
     </row>
   </sheetData>
@@ -12734,11 +12778,11 @@
         <v>210</v>
       </c>
       <c r="C2" t="n">
-        <v>188.03</v>
+        <v>188.4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -12753,7 +12797,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -12768,7 +12812,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -12786,7 +12830,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -12804,7 +12848,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -12818,11 +12862,11 @@
         <v>280</v>
       </c>
       <c r="C7" t="n">
-        <v>270.86</v>
+        <v>271.21</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -12836,11 +12880,11 @@
         <v>218.5</v>
       </c>
       <c r="C8" t="n">
-        <v>216.6</v>
+        <v>216.68</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -12854,11 +12898,11 @@
         <v>193</v>
       </c>
       <c r="C9" t="n">
-        <v>186.43</v>
+        <v>186.5</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -12870,7 +12914,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>

--- a/output/Data and Chart Outputs/philippines_dam_levels.xlsx
+++ b/output/Data and Chart Outputs/philippines_dam_levels.xlsx
@@ -156,7 +156,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Angat dam water level (Metro Manila water supply and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-07</a:t>
+              <a:t>Angat dam water level (Metro Manila water supply and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-08</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -426,7 +426,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>San Roque dam water level (hydro, Agno river; PAGASA) - water year (Oct-Sep), data to 2026-10-07</a:t>
+              <a:t>San Roque dam water level (hydro, Agno river; PAGASA) - water year (Oct-Sep), data to 2026-10-08</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -696,7 +696,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Magat dam water level (irrigation and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-07</a:t>
+              <a:t>Magat dam water level (irrigation and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-08</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -966,7 +966,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Pantabangan dam water level (irrigation and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-07</a:t>
+              <a:t>Pantabangan dam water level (irrigation and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-08</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1659,7 +1659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Daily from 2026-10-02 to 2026-10-07 - PAGASA posts only today's and yesterday's readings, so the history here starts with this pull's first run. Luzon reservoirs: Angat (Metro Manila water supply, 218 MW hydro), Ipo and La Mesa (water supply), Ambuklao, Binga, San Roque (hydro, Agno river), Pantabangan and Magat (irrigation + hydro), Caliraya (pumped storage).</t>
+          <t>Daily from 2026-10-02 to 2026-10-08 - PAGASA posts only today's and yesterday's readings, so the history here starts with this pull's first run. Luzon reservoirs: Angat (Metro Manila water supply, 218 MW hydro), Ipo and La Mesa (water supply), Ambuklao, Binga, San Roque (hydro, Agno river), Pantabangan and Magat (irrigation + hydro), Caliraya (pumped storage).</t>
         </is>
       </c>
     </row>
@@ -1820,6 +1820,9 @@
         <is>
           <t>08-Oct</t>
         </is>
+      </c>
+      <c r="G9" t="n">
+        <v>207.83</v>
       </c>
     </row>
     <row r="10">
@@ -4520,6 +4523,9 @@
           <t>08-Oct</t>
         </is>
       </c>
+      <c r="G9" t="n">
+        <v>283.12</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7219,6 +7225,9 @@
           <t>08-Oct</t>
         </is>
       </c>
+      <c r="G9" t="n">
+        <v>191.5</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -9918,6 +9927,9 @@
           <t>08-Oct</t>
         </is>
       </c>
+      <c r="G9" t="n">
+        <v>208.81</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12485,7 +12497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12730,6 +12742,38 @@
       </c>
       <c r="J7" t="n">
         <v>286.28</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B8" t="n">
+        <v>207.83</v>
+      </c>
+      <c r="C8" t="n">
+        <v>100.65</v>
+      </c>
+      <c r="D8" t="n">
+        <v>79.38</v>
+      </c>
+      <c r="E8" t="n">
+        <v>751.47</v>
+      </c>
+      <c r="F8" t="n">
+        <v>574.21</v>
+      </c>
+      <c r="G8" t="n">
+        <v>283.12</v>
+      </c>
+      <c r="H8" t="n">
+        <v>208.81</v>
+      </c>
+      <c r="I8" t="n">
+        <v>191.5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>286.27</v>
       </c>
     </row>
   </sheetData>
@@ -12778,11 +12822,11 @@
         <v>210</v>
       </c>
       <c r="C2" t="n">
-        <v>188.4</v>
+        <v>188.77</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>
@@ -12797,7 +12841,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>
@@ -12812,7 +12856,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>
@@ -12830,7 +12874,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>
@@ -12848,7 +12892,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>
@@ -12862,11 +12906,11 @@
         <v>280</v>
       </c>
       <c r="C7" t="n">
-        <v>271.21</v>
+        <v>271.56</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>
@@ -12880,11 +12924,11 @@
         <v>218.5</v>
       </c>
       <c r="C8" t="n">
-        <v>216.68</v>
+        <v>216.77</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>
@@ -12898,11 +12942,11 @@
         <v>193</v>
       </c>
       <c r="C9" t="n">
-        <v>186.5</v>
+        <v>186.57</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12958,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>

--- a/output/Data and Chart Outputs/philippines_dam_levels.xlsx
+++ b/output/Data and Chart Outputs/philippines_dam_levels.xlsx
@@ -156,7 +156,8 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Angat dam water level (Metro Manila water supply and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-08</a:t>
+              <a:rPr sz="1200" b="1"/>
+              <a:t>Angat dam water level (Metro Manila water supply and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-09</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -268,7 +269,7 @@
           <spPr>
             <a:ln w="19050">
               <a:solidFill>
-                <a:srgbClr val="EB6834"/>
+                <a:srgbClr val="2A78D6"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -389,7 +390,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
-        <majorUnit val="0.1"/>
+        <majorUnit val="0.2"/>
       </valAx>
       <spPr>
         <a:ln>
@@ -426,7 +427,8 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>San Roque dam water level (hydro, Agno river; PAGASA) - water year (Oct-Sep), data to 2026-10-08</a:t>
+              <a:rPr sz="1200" b="1"/>
+              <a:t>San Roque dam water level (hydro, Agno river; PAGASA) - water year (Oct-Sep), data to 2026-10-09</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -538,7 +540,7 @@
           <spPr>
             <a:ln w="19050">
               <a:solidFill>
-                <a:srgbClr val="EB6834"/>
+                <a:srgbClr val="2A78D6"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -696,7 +698,8 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Magat dam water level (irrigation and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-08</a:t>
+              <a:rPr sz="1200" b="1"/>
+              <a:t>Magat dam water level (irrigation and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-09</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -808,7 +811,7 @@
           <spPr>
             <a:ln w="19050">
               <a:solidFill>
-                <a:srgbClr val="EB6834"/>
+                <a:srgbClr val="2A78D6"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -966,7 +969,8 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Pantabangan dam water level (irrigation and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-08</a:t>
+              <a:rPr sz="1200" b="1"/>
+              <a:t>Pantabangan dam water level (irrigation and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-09</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1078,7 +1082,7 @@
           <spPr>
             <a:ln w="19050">
               <a:solidFill>
-                <a:srgbClr val="EB6834"/>
+                <a:srgbClr val="2A78D6"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1659,7 +1663,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Daily from 2026-10-02 to 2026-10-08 - PAGASA posts only today's and yesterday's readings, so the history here starts with this pull's first run. Luzon reservoirs: Angat (Metro Manila water supply, 218 MW hydro), Ipo and La Mesa (water supply), Ambuklao, Binga, San Roque (hydro, Agno river), Pantabangan and Magat (irrigation + hydro), Caliraya (pumped storage).</t>
+          <t>Daily from 2026-10-02 to 2026-10-09 - PAGASA posts only today's and yesterday's readings, so the history here starts with this pull's first run. Luzon reservoirs: Angat (Metro Manila water supply, 218 MW hydro), Ipo and La Mesa (water supply), Ambuklao, Binga, San Roque (hydro, Agno river), Pantabangan and Magat (irrigation + hydro), Caliraya (pumped storage).</t>
         </is>
       </c>
     </row>
@@ -1830,6 +1834,9 @@
         <is>
           <t>09-Oct</t>
         </is>
+      </c>
+      <c r="G10" t="n">
+        <v>207.8</v>
       </c>
     </row>
     <row r="11">
@@ -4533,6 +4540,9 @@
           <t>09-Oct</t>
         </is>
       </c>
+      <c r="G10" t="n">
+        <v>283.23</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -7235,6 +7245,9 @@
           <t>09-Oct</t>
         </is>
       </c>
+      <c r="G10" t="n">
+        <v>191.81</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -9937,6 +9950,9 @@
           <t>09-Oct</t>
         </is>
       </c>
+      <c r="G10" t="n">
+        <v>208.97</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -12497,7 +12513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12774,6 +12790,38 @@
       </c>
       <c r="J8" t="n">
         <v>286.27</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B9" t="n">
+        <v>207.8</v>
+      </c>
+      <c r="C9" t="n">
+        <v>100.26</v>
+      </c>
+      <c r="D9" t="n">
+        <v>79.42</v>
+      </c>
+      <c r="E9" t="n">
+        <v>751.3200000000001</v>
+      </c>
+      <c r="F9" t="n">
+        <v>574.29</v>
+      </c>
+      <c r="G9" t="n">
+        <v>283.23</v>
+      </c>
+      <c r="H9" t="n">
+        <v>208.97</v>
+      </c>
+      <c r="I9" t="n">
+        <v>191.81</v>
+      </c>
+      <c r="J9" t="n">
+        <v>286.35</v>
       </c>
     </row>
   </sheetData>
@@ -12822,11 +12870,11 @@
         <v>210</v>
       </c>
       <c r="C2" t="n">
-        <v>188.77</v>
+        <v>189.14</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
     </row>
@@ -12841,7 +12889,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
     </row>
@@ -12856,7 +12904,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
     </row>
@@ -12874,7 +12922,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
     </row>
@@ -12892,7 +12940,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
     </row>
@@ -12906,11 +12954,11 @@
         <v>280</v>
       </c>
       <c r="C7" t="n">
-        <v>271.56</v>
+        <v>271.91</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
     </row>
@@ -12924,11 +12972,11 @@
         <v>218.5</v>
       </c>
       <c r="C8" t="n">
-        <v>216.77</v>
+        <v>216.85</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
     </row>
@@ -12942,11 +12990,11 @@
         <v>193</v>
       </c>
       <c r="C9" t="n">
-        <v>186.57</v>
+        <v>186.64</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
     </row>
@@ -12958,7 +13006,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
     </row>

--- a/output/Data and Chart Outputs/philippines_dam_levels.xlsx
+++ b/output/Data and Chart Outputs/philippines_dam_levels.xlsx
@@ -157,7 +157,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Angat dam water level (Metro Manila water supply and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-09</a:t>
+              <a:t>Angat dam water level (Metro Manila water supply and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-10</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -428,7 +428,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>San Roque dam water level (hydro, Agno river; PAGASA) - water year (Oct-Sep), data to 2026-10-09</a:t>
+              <a:t>San Roque dam water level (hydro, Agno river; PAGASA) - water year (Oct-Sep), data to 2026-10-10</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -699,7 +699,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Magat dam water level (irrigation and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-09</a:t>
+              <a:t>Magat dam water level (irrigation and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-10</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -970,7 +970,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Pantabangan dam water level (irrigation and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-09</a:t>
+              <a:t>Pantabangan dam water level (irrigation and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-10</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1177,7 +1177,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="209"/>
+          <max val="210"/>
           <min val="207"/>
         </scaling>
         <delete val="0"/>
@@ -1663,7 +1663,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Daily from 2026-10-02 to 2026-10-09 - PAGASA posts only today's and yesterday's readings, so the history here starts with this pull's first run. Luzon reservoirs: Angat (Metro Manila water supply, 218 MW hydro), Ipo and La Mesa (water supply), Ambuklao, Binga, San Roque (hydro, Agno river), Pantabangan and Magat (irrigation + hydro), Caliraya (pumped storage).</t>
+          <t>Daily from 2026-10-02 to 2026-10-10 - PAGASA posts only today's and yesterday's readings, so the history here starts with this pull's first run. Luzon reservoirs: Angat (Metro Manila water supply, 218 MW hydro), Ipo and La Mesa (water supply), Ambuklao, Binga, San Roque (hydro, Agno river), Pantabangan and Magat (irrigation + hydro), Caliraya (pumped storage).</t>
         </is>
       </c>
     </row>
@@ -1844,6 +1844,9 @@
         <is>
           <t>10-Oct</t>
         </is>
+      </c>
+      <c r="G11" t="n">
+        <v>207.68</v>
       </c>
     </row>
     <row r="12">
@@ -4550,6 +4553,9 @@
           <t>10-Oct</t>
         </is>
       </c>
+      <c r="G11" t="n">
+        <v>283.35</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -7255,6 +7261,9 @@
           <t>10-Oct</t>
         </is>
       </c>
+      <c r="G11" t="n">
+        <v>191.98</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -9960,6 +9969,9 @@
           <t>10-Oct</t>
         </is>
       </c>
+      <c r="G11" t="n">
+        <v>209.06</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -12513,7 +12525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12822,6 +12834,38 @@
       </c>
       <c r="J9" t="n">
         <v>286.35</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B10" t="n">
+        <v>207.68</v>
+      </c>
+      <c r="C10" t="n">
+        <v>100.16</v>
+      </c>
+      <c r="D10" t="n">
+        <v>79.44</v>
+      </c>
+      <c r="E10" t="n">
+        <v>751.0700000000001</v>
+      </c>
+      <c r="F10" t="n">
+        <v>574.08</v>
+      </c>
+      <c r="G10" t="n">
+        <v>283.35</v>
+      </c>
+      <c r="H10" t="n">
+        <v>209.06</v>
+      </c>
+      <c r="I10" t="n">
+        <v>191.98</v>
+      </c>
+      <c r="J10" t="n">
+        <v>286.21</v>
       </c>
     </row>
   </sheetData>
@@ -12870,11 +12914,11 @@
         <v>210</v>
       </c>
       <c r="C2" t="n">
-        <v>189.14</v>
+        <v>189.51</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -12889,7 +12933,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -12904,7 +12948,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -12922,7 +12966,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -12940,7 +12984,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -12954,11 +12998,11 @@
         <v>280</v>
       </c>
       <c r="C7" t="n">
-        <v>271.91</v>
+        <v>272.26</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -12972,11 +13016,11 @@
         <v>218.5</v>
       </c>
       <c r="C8" t="n">
-        <v>216.85</v>
+        <v>216.93</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -12990,11 +13034,11 @@
         <v>193</v>
       </c>
       <c r="C9" t="n">
-        <v>186.64</v>
+        <v>186.71</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -13006,7 +13050,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>

--- a/output/Data and Chart Outputs/philippines_dam_levels.xlsx
+++ b/output/Data and Chart Outputs/philippines_dam_levels.xlsx
@@ -157,7 +157,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Angat dam water level (Metro Manila water supply and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-10</a:t>
+              <a:t>Angat dam water level (Metro Manila water supply and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-11</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -428,7 +428,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>San Roque dam water level (hydro, Agno river; PAGASA) - water year (Oct-Sep), data to 2026-10-10</a:t>
+              <a:t>San Roque dam water level (hydro, Agno river; PAGASA) - water year (Oct-Sep), data to 2026-10-11</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -699,7 +699,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Magat dam water level (irrigation and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-10</a:t>
+              <a:t>Magat dam water level (irrigation and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-11</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -906,7 +906,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="192"/>
+          <max val="193"/>
           <min val="189"/>
         </scaling>
         <delete val="0"/>
@@ -970,7 +970,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Pantabangan dam water level (irrigation and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-10</a:t>
+              <a:t>Pantabangan dam water level (irrigation and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-11</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1663,7 +1663,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Daily from 2026-10-02 to 2026-10-10 - PAGASA posts only today's and yesterday's readings, so the history here starts with this pull's first run. Luzon reservoirs: Angat (Metro Manila water supply, 218 MW hydro), Ipo and La Mesa (water supply), Ambuklao, Binga, San Roque (hydro, Agno river), Pantabangan and Magat (irrigation + hydro), Caliraya (pumped storage).</t>
+          <t>Daily from 2026-10-02 to 2026-10-11 - PAGASA posts only today's and yesterday's readings, so the history here starts with this pull's first run. Luzon reservoirs: Angat (Metro Manila water supply, 218 MW hydro), Ipo and La Mesa (water supply), Ambuklao, Binga, San Roque (hydro, Agno river), Pantabangan and Magat (irrigation + hydro), Caliraya (pumped storage).</t>
         </is>
       </c>
     </row>
@@ -1854,6 +1854,9 @@
         <is>
           <t>11-Oct</t>
         </is>
+      </c>
+      <c r="G12" t="n">
+        <v>207.7</v>
       </c>
     </row>
     <row r="13">
@@ -4563,6 +4566,9 @@
           <t>11-Oct</t>
         </is>
       </c>
+      <c r="G12" t="n">
+        <v>283.39</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -7271,6 +7277,9 @@
           <t>11-Oct</t>
         </is>
       </c>
+      <c r="G12" t="n">
+        <v>192.1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -9979,6 +9988,9 @@
           <t>11-Oct</t>
         </is>
       </c>
+      <c r="G12" t="n">
+        <v>209.16</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -12525,7 +12537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12866,6 +12878,38 @@
       </c>
       <c r="J10" t="n">
         <v>286.21</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B11" t="n">
+        <v>207.7</v>
+      </c>
+      <c r="C11" t="n">
+        <v>100.07</v>
+      </c>
+      <c r="D11" t="n">
+        <v>79.45</v>
+      </c>
+      <c r="E11" t="n">
+        <v>750.72</v>
+      </c>
+      <c r="F11" t="n">
+        <v>573.86</v>
+      </c>
+      <c r="G11" t="n">
+        <v>283.39</v>
+      </c>
+      <c r="H11" t="n">
+        <v>209.16</v>
+      </c>
+      <c r="I11" t="n">
+        <v>192.1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>286.16</v>
       </c>
     </row>
   </sheetData>
@@ -12914,11 +12958,11 @@
         <v>210</v>
       </c>
       <c r="C2" t="n">
-        <v>189.51</v>
+        <v>189.88</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -12933,7 +12977,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -12948,7 +12992,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -12966,7 +13010,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -12984,7 +13028,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -12998,11 +13042,11 @@
         <v>280</v>
       </c>
       <c r="C7" t="n">
-        <v>272.26</v>
+        <v>272.62</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -13016,11 +13060,11 @@
         <v>218.5</v>
       </c>
       <c r="C8" t="n">
-        <v>216.93</v>
+        <v>217.02</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -13034,11 +13078,11 @@
         <v>193</v>
       </c>
       <c r="C9" t="n">
-        <v>186.71</v>
+        <v>186.78</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -13050,7 +13094,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>

--- a/output/Data and Chart Outputs/philippines_dam_levels.xlsx
+++ b/output/Data and Chart Outputs/philippines_dam_levels.xlsx
@@ -157,7 +157,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Angat dam water level (Metro Manila water supply and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-11</a:t>
+              <a:t>Angat dam water level (Metro Manila water supply and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-12</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -428,7 +428,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>San Roque dam water level (hydro, Agno river; PAGASA) - water year (Oct-Sep), data to 2026-10-11</a:t>
+              <a:t>San Roque dam water level (hydro, Agno river; PAGASA) - water year (Oct-Sep), data to 2026-10-12</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -699,7 +699,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Magat dam water level (irrigation and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-11</a:t>
+              <a:t>Magat dam water level (irrigation and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-12</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -970,7 +970,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Pantabangan dam water level (irrigation and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-11</a:t>
+              <a:t>Pantabangan dam water level (irrigation and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-12</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1663,7 +1663,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Daily from 2026-10-02 to 2026-10-11 - PAGASA posts only today's and yesterday's readings, so the history here starts with this pull's first run. Luzon reservoirs: Angat (Metro Manila water supply, 218 MW hydro), Ipo and La Mesa (water supply), Ambuklao, Binga, San Roque (hydro, Agno river), Pantabangan and Magat (irrigation + hydro), Caliraya (pumped storage).</t>
+          <t>Daily from 2026-10-02 to 2026-10-12 - PAGASA posts only today's and yesterday's readings, so the history here starts with this pull's first run. Luzon reservoirs: Angat (Metro Manila water supply, 218 MW hydro), Ipo and La Mesa (water supply), Ambuklao, Binga, San Roque (hydro, Agno river), Pantabangan and Magat (irrigation + hydro), Caliraya (pumped storage).</t>
         </is>
       </c>
     </row>
@@ -1864,6 +1864,9 @@
         <is>
           <t>12-Oct</t>
         </is>
+      </c>
+      <c r="G13" t="n">
+        <v>208.29</v>
       </c>
     </row>
     <row r="14">
@@ -4576,6 +4579,9 @@
           <t>12-Oct</t>
         </is>
       </c>
+      <c r="G13" t="n">
+        <v>283.69</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -7287,6 +7293,9 @@
           <t>12-Oct</t>
         </is>
       </c>
+      <c r="G13" t="n">
+        <v>192.22</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -9998,6 +10007,9 @@
           <t>12-Oct</t>
         </is>
       </c>
+      <c r="G13" t="n">
+        <v>209.28</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -12537,7 +12549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12910,6 +12922,38 @@
       </c>
       <c r="J11" t="n">
         <v>286.16</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B12" t="n">
+        <v>208.29</v>
+      </c>
+      <c r="C12" t="n">
+        <v>100.35</v>
+      </c>
+      <c r="D12" t="n">
+        <v>79.52</v>
+      </c>
+      <c r="E12" t="n">
+        <v>750.54</v>
+      </c>
+      <c r="F12" t="n">
+        <v>573.91</v>
+      </c>
+      <c r="G12" t="n">
+        <v>283.69</v>
+      </c>
+      <c r="H12" t="n">
+        <v>209.28</v>
+      </c>
+      <c r="I12" t="n">
+        <v>192.22</v>
+      </c>
+      <c r="J12" t="n">
+        <v>286.61</v>
       </c>
     </row>
   </sheetData>
@@ -12958,11 +13002,11 @@
         <v>210</v>
       </c>
       <c r="C2" t="n">
-        <v>189.88</v>
+        <v>190.25</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -12977,7 +13021,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -12992,7 +13036,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -13010,7 +13054,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -13028,7 +13072,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -13042,11 +13086,11 @@
         <v>280</v>
       </c>
       <c r="C7" t="n">
-        <v>272.62</v>
+        <v>272.97</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -13060,11 +13104,11 @@
         <v>218.5</v>
       </c>
       <c r="C8" t="n">
-        <v>217.02</v>
+        <v>217.1</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -13078,11 +13122,11 @@
         <v>193</v>
       </c>
       <c r="C9" t="n">
-        <v>186.78</v>
+        <v>186.86</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -13094,7 +13138,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>

--- a/output/Data and Chart Outputs/philippines_dam_levels.xlsx
+++ b/output/Data and Chart Outputs/philippines_dam_levels.xlsx
@@ -157,7 +157,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Angat dam water level (Metro Manila water supply and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-12</a:t>
+              <a:t>Angat dam water level (Metro Manila water supply and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-28</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -364,7 +364,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="209"/>
+          <max val="210"/>
           <min val="207"/>
         </scaling>
         <delete val="0"/>
@@ -428,7 +428,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>San Roque dam water level (hydro, Agno river; PAGASA) - water year (Oct-Sep), data to 2026-10-12</a:t>
+              <a:t>San Roque dam water level (hydro, Agno river; PAGASA) - water year (Oct-Sep), data to 2026-10-28</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -636,7 +636,7 @@
         <scaling>
           <orientation val="minMax"/>
           <max val="284"/>
-          <min val="282"/>
+          <min val="281"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -661,7 +661,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
-        <majorUnit val="0.2"/>
+        <majorUnit val="0.5"/>
       </valAx>
       <spPr>
         <a:ln>
@@ -699,7 +699,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Magat dam water level (irrigation and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-12</a:t>
+              <a:t>Magat dam water level (irrigation and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-28</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -970,7 +970,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Pantabangan dam water level (irrigation and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-12</a:t>
+              <a:t>Pantabangan dam water level (irrigation and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-28</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1177,7 +1177,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="210"/>
+          <max val="211"/>
           <min val="207"/>
         </scaling>
         <delete val="0"/>
@@ -1203,7 +1203,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
-        <majorUnit val="0.2"/>
+        <majorUnit val="0.5"/>
       </valAx>
       <spPr>
         <a:ln>
@@ -1663,7 +1663,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Daily from 2026-10-02 to 2026-10-12 - PAGASA posts only today's and yesterday's readings, so the history here starts with this pull's first run. Luzon reservoirs: Angat (Metro Manila water supply, 218 MW hydro), Ipo and La Mesa (water supply), Ambuklao, Binga, San Roque (hydro, Agno river), Pantabangan and Magat (irrigation + hydro), Caliraya (pumped storage).</t>
+          <t>Daily from 2026-10-02 to 2026-10-28 - PAGASA posts only today's and yesterday's readings, so the history here starts with this pull's first run. Luzon reservoirs: Angat (Metro Manila water supply, 218 MW hydro), Ipo and La Mesa (water supply), Ambuklao, Binga, San Roque (hydro, Agno river), Pantabangan and Magat (irrigation + hydro), Caliraya (pumped storage).</t>
         </is>
       </c>
     </row>
@@ -1875,6 +1875,9 @@
           <t>13-Oct</t>
         </is>
       </c>
+      <c r="G14" t="n">
+        <v>208.34</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1882,6 +1885,9 @@
           <t>14-Oct</t>
         </is>
       </c>
+      <c r="G15" t="n">
+        <v>208.39</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1889,6 +1895,9 @@
           <t>15-Oct</t>
         </is>
       </c>
+      <c r="G16" t="n">
+        <v>208.44</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1896,6 +1905,9 @@
           <t>16-Oct</t>
         </is>
       </c>
+      <c r="G17" t="n">
+        <v>208.49</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1903,6 +1915,9 @@
           <t>17-Oct</t>
         </is>
       </c>
+      <c r="G18" t="n">
+        <v>208.54</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1910,6 +1925,9 @@
           <t>18-Oct</t>
         </is>
       </c>
+      <c r="G19" t="n">
+        <v>208.59</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1917,6 +1935,9 @@
           <t>19-Oct</t>
         </is>
       </c>
+      <c r="G20" t="n">
+        <v>208.64</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1924,6 +1945,9 @@
           <t>20-Oct</t>
         </is>
       </c>
+      <c r="G21" t="n">
+        <v>208.68</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1931,6 +1955,9 @@
           <t>21-Oct</t>
         </is>
       </c>
+      <c r="G22" t="n">
+        <v>208.73</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1938,6 +1965,9 @@
           <t>22-Oct</t>
         </is>
       </c>
+      <c r="G23" t="n">
+        <v>208.78</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1945,6 +1975,9 @@
           <t>23-Oct</t>
         </is>
       </c>
+      <c r="G24" t="n">
+        <v>208.83</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1952,6 +1985,9 @@
           <t>24-Oct</t>
         </is>
       </c>
+      <c r="G25" t="n">
+        <v>208.88</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1959,6 +1995,9 @@
           <t>25-Oct</t>
         </is>
       </c>
+      <c r="G26" t="n">
+        <v>208.93</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1966,6 +2005,9 @@
           <t>26-Oct</t>
         </is>
       </c>
+      <c r="G27" t="n">
+        <v>208.98</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1973,12 +2015,18 @@
           <t>27-Oct</t>
         </is>
       </c>
+      <c r="G28" t="n">
+        <v>209.03</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
           <t>28-Oct</t>
         </is>
+      </c>
+      <c r="G29" t="n">
+        <v>208.94</v>
       </c>
     </row>
     <row r="30">
@@ -4589,6 +4637,9 @@
           <t>13-Oct</t>
         </is>
       </c>
+      <c r="G14" t="n">
+        <v>283.55</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4596,6 +4647,9 @@
           <t>14-Oct</t>
         </is>
       </c>
+      <c r="G15" t="n">
+        <v>283.41</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4603,6 +4657,9 @@
           <t>15-Oct</t>
         </is>
       </c>
+      <c r="G16" t="n">
+        <v>283.28</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4610,6 +4667,9 @@
           <t>16-Oct</t>
         </is>
       </c>
+      <c r="G17" t="n">
+        <v>283.14</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4617,6 +4677,9 @@
           <t>17-Oct</t>
         </is>
       </c>
+      <c r="G18" t="n">
+        <v>283</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4624,6 +4687,9 @@
           <t>18-Oct</t>
         </is>
       </c>
+      <c r="G19" t="n">
+        <v>282.86</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4631,6 +4697,9 @@
           <t>19-Oct</t>
         </is>
       </c>
+      <c r="G20" t="n">
+        <v>282.72</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4638,6 +4707,9 @@
           <t>20-Oct</t>
         </is>
       </c>
+      <c r="G21" t="n">
+        <v>282.59</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4645,6 +4717,9 @@
           <t>21-Oct</t>
         </is>
       </c>
+      <c r="G22" t="n">
+        <v>282.45</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4652,6 +4727,9 @@
           <t>22-Oct</t>
         </is>
       </c>
+      <c r="G23" t="n">
+        <v>282.31</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4659,6 +4737,9 @@
           <t>23-Oct</t>
         </is>
       </c>
+      <c r="G24" t="n">
+        <v>282.17</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4666,6 +4747,9 @@
           <t>24-Oct</t>
         </is>
       </c>
+      <c r="G25" t="n">
+        <v>282.03</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4673,6 +4757,9 @@
           <t>25-Oct</t>
         </is>
       </c>
+      <c r="G26" t="n">
+        <v>281.9</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4680,6 +4767,9 @@
           <t>26-Oct</t>
         </is>
       </c>
+      <c r="G27" t="n">
+        <v>281.76</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4687,12 +4777,18 @@
           <t>27-Oct</t>
         </is>
       </c>
+      <c r="G28" t="n">
+        <v>281.62</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
           <t>28-Oct</t>
         </is>
+      </c>
+      <c r="G29" t="n">
+        <v>281.63</v>
       </c>
     </row>
     <row r="30">
@@ -7303,6 +7399,9 @@
           <t>13-Oct</t>
         </is>
       </c>
+      <c r="G14" t="n">
+        <v>192.09</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -7310,6 +7409,9 @@
           <t>14-Oct</t>
         </is>
       </c>
+      <c r="G15" t="n">
+        <v>191.97</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -7317,6 +7419,9 @@
           <t>15-Oct</t>
         </is>
       </c>
+      <c r="G16" t="n">
+        <v>191.84</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -7324,6 +7429,9 @@
           <t>16-Oct</t>
         </is>
       </c>
+      <c r="G17" t="n">
+        <v>191.71</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -7331,6 +7439,9 @@
           <t>17-Oct</t>
         </is>
       </c>
+      <c r="G18" t="n">
+        <v>191.58</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -7338,6 +7449,9 @@
           <t>18-Oct</t>
         </is>
       </c>
+      <c r="G19" t="n">
+        <v>191.46</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -7345,6 +7459,9 @@
           <t>19-Oct</t>
         </is>
       </c>
+      <c r="G20" t="n">
+        <v>191.33</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -7352,6 +7469,9 @@
           <t>20-Oct</t>
         </is>
       </c>
+      <c r="G21" t="n">
+        <v>191.2</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -7359,6 +7479,9 @@
           <t>21-Oct</t>
         </is>
       </c>
+      <c r="G22" t="n">
+        <v>191.07</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -7366,6 +7489,9 @@
           <t>22-Oct</t>
         </is>
       </c>
+      <c r="G23" t="n">
+        <v>190.95</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -7373,6 +7499,9 @@
           <t>23-Oct</t>
         </is>
       </c>
+      <c r="G24" t="n">
+        <v>190.82</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -7380,6 +7509,9 @@
           <t>24-Oct</t>
         </is>
       </c>
+      <c r="G25" t="n">
+        <v>190.69</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -7387,6 +7519,9 @@
           <t>25-Oct</t>
         </is>
       </c>
+      <c r="G26" t="n">
+        <v>190.56</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -7394,6 +7529,9 @@
           <t>26-Oct</t>
         </is>
       </c>
+      <c r="G27" t="n">
+        <v>190.44</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -7401,12 +7539,18 @@
           <t>27-Oct</t>
         </is>
       </c>
+      <c r="G28" t="n">
+        <v>190.31</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
           <t>28-Oct</t>
         </is>
+      </c>
+      <c r="G29" t="n">
+        <v>190.11</v>
       </c>
     </row>
     <row r="30">
@@ -10017,6 +10161,9 @@
           <t>13-Oct</t>
         </is>
       </c>
+      <c r="G14" t="n">
+        <v>209.34</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -10024,6 +10171,9 @@
           <t>14-Oct</t>
         </is>
       </c>
+      <c r="G15" t="n">
+        <v>209.4</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -10031,6 +10181,9 @@
           <t>15-Oct</t>
         </is>
       </c>
+      <c r="G16" t="n">
+        <v>209.46</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -10038,6 +10191,9 @@
           <t>16-Oct</t>
         </is>
       </c>
+      <c r="G17" t="n">
+        <v>209.52</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -10045,6 +10201,9 @@
           <t>17-Oct</t>
         </is>
       </c>
+      <c r="G18" t="n">
+        <v>209.58</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -10052,6 +10211,9 @@
           <t>18-Oct</t>
         </is>
       </c>
+      <c r="G19" t="n">
+        <v>209.64</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -10059,6 +10221,9 @@
           <t>19-Oct</t>
         </is>
       </c>
+      <c r="G20" t="n">
+        <v>209.7</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -10066,6 +10231,9 @@
           <t>20-Oct</t>
         </is>
       </c>
+      <c r="G21" t="n">
+        <v>209.75</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -10073,6 +10241,9 @@
           <t>21-Oct</t>
         </is>
       </c>
+      <c r="G22" t="n">
+        <v>209.81</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -10080,6 +10251,9 @@
           <t>22-Oct</t>
         </is>
       </c>
+      <c r="G23" t="n">
+        <v>209.87</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -10087,6 +10261,9 @@
           <t>23-Oct</t>
         </is>
       </c>
+      <c r="G24" t="n">
+        <v>209.93</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -10094,6 +10271,9 @@
           <t>24-Oct</t>
         </is>
       </c>
+      <c r="G25" t="n">
+        <v>209.99</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -10101,6 +10281,9 @@
           <t>25-Oct</t>
         </is>
       </c>
+      <c r="G26" t="n">
+        <v>210.05</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -10108,6 +10291,9 @@
           <t>26-Oct</t>
         </is>
       </c>
+      <c r="G27" t="n">
+        <v>210.11</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -10115,12 +10301,18 @@
           <t>27-Oct</t>
         </is>
       </c>
+      <c r="G28" t="n">
+        <v>210.17</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
           <t>28-Oct</t>
         </is>
+      </c>
+      <c r="G29" t="n">
+        <v>210.21</v>
       </c>
     </row>
     <row r="30">
@@ -12549,7 +12741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12954,6 +13146,70 @@
       </c>
       <c r="J12" t="n">
         <v>286.61</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B13" t="n">
+        <v>209.03</v>
+      </c>
+      <c r="C13" t="n">
+        <v>100.84</v>
+      </c>
+      <c r="D13" t="n">
+        <v>79.31</v>
+      </c>
+      <c r="E13" t="n">
+        <v>751.7</v>
+      </c>
+      <c r="F13" t="n">
+        <v>574.74</v>
+      </c>
+      <c r="G13" t="n">
+        <v>281.62</v>
+      </c>
+      <c r="H13" t="n">
+        <v>210.17</v>
+      </c>
+      <c r="I13" t="n">
+        <v>190.31</v>
+      </c>
+      <c r="J13" t="n">
+        <v>286.64</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B14" t="n">
+        <v>208.94</v>
+      </c>
+      <c r="C14" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="D14" t="n">
+        <v>79.34999999999999</v>
+      </c>
+      <c r="E14" t="n">
+        <v>751.64</v>
+      </c>
+      <c r="F14" t="n">
+        <v>574.6799999999999</v>
+      </c>
+      <c r="G14" t="n">
+        <v>281.63</v>
+      </c>
+      <c r="H14" t="n">
+        <v>210.21</v>
+      </c>
+      <c r="I14" t="n">
+        <v>190.11</v>
+      </c>
+      <c r="J14" t="n">
+        <v>286.56</v>
       </c>
     </row>
   </sheetData>
@@ -13002,11 +13258,11 @@
         <v>210</v>
       </c>
       <c r="C2" t="n">
-        <v>190.25</v>
+        <v>196.19</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -13021,7 +13277,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -13036,7 +13292,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -13050,11 +13306,11 @@
         <v>752</v>
       </c>
       <c r="C5" t="n">
-        <v>745</v>
+        <v>750.6900000000001</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -13068,11 +13324,11 @@
         <v>575</v>
       </c>
       <c r="C6" t="n">
-        <v>565</v>
+        <v>573.13</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -13086,11 +13342,11 @@
         <v>280</v>
       </c>
       <c r="C7" t="n">
-        <v>272.97</v>
+        <v>278.59</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -13101,14 +13357,14 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>218.5</v>
+        <v>221</v>
       </c>
       <c r="C8" t="n">
-        <v>217.1</v>
+        <v>218.42</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -13122,11 +13378,11 @@
         <v>193</v>
       </c>
       <c r="C9" t="n">
-        <v>186.86</v>
+        <v>188</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -13138,7 +13394,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>

--- a/output/Data and Chart Outputs/philippines_dam_levels.xlsx
+++ b/output/Data and Chart Outputs/philippines_dam_levels.xlsx
@@ -157,7 +157,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Angat dam water level (Metro Manila water supply and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-28</a:t>
+              <a:t>Angat dam water level (Metro Manila water supply and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-29</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -428,7 +428,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>San Roque dam water level (hydro, Agno river; PAGASA) - water year (Oct-Sep), data to 2026-10-28</a:t>
+              <a:t>San Roque dam water level (hydro, Agno river; PAGASA) - water year (Oct-Sep), data to 2026-10-29</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -699,7 +699,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Magat dam water level (irrigation and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-28</a:t>
+              <a:t>Magat dam water level (irrigation and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-29</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -970,7 +970,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Pantabangan dam water level (irrigation and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-28</a:t>
+              <a:t>Pantabangan dam water level (irrigation and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-29</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1663,7 +1663,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Daily from 2026-10-02 to 2026-10-28 - PAGASA posts only today's and yesterday's readings, so the history here starts with this pull's first run. Luzon reservoirs: Angat (Metro Manila water supply, 218 MW hydro), Ipo and La Mesa (water supply), Ambuklao, Binga, San Roque (hydro, Agno river), Pantabangan and Magat (irrigation + hydro), Caliraya (pumped storage).</t>
+          <t>Daily from 2026-10-02 to 2026-10-29 - PAGASA posts only today's and yesterday's readings, so the history here starts with this pull's first run. Luzon reservoirs: Angat (Metro Manila water supply, 218 MW hydro), Ipo and La Mesa (water supply), Ambuklao, Binga, San Roque (hydro, Agno river), Pantabangan and Magat (irrigation + hydro), Caliraya (pumped storage).</t>
         </is>
       </c>
     </row>
@@ -2034,6 +2034,9 @@
         <is>
           <t>29-Oct</t>
         </is>
+      </c>
+      <c r="G30" t="n">
+        <v>208.76</v>
       </c>
     </row>
     <row r="31">
@@ -4797,6 +4800,9 @@
           <t>29-Oct</t>
         </is>
       </c>
+      <c r="G30" t="n">
+        <v>281.65</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -7559,6 +7565,9 @@
           <t>29-Oct</t>
         </is>
       </c>
+      <c r="G30" t="n">
+        <v>189.97</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -10321,6 +10330,9 @@
           <t>29-Oct</t>
         </is>
       </c>
+      <c r="G30" t="n">
+        <v>210.24</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -12741,7 +12753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13210,6 +13222,38 @@
       </c>
       <c r="J14" t="n">
         <v>286.56</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B15" t="n">
+        <v>208.76</v>
+      </c>
+      <c r="C15" t="n">
+        <v>100.46</v>
+      </c>
+      <c r="D15" t="n">
+        <v>79.39</v>
+      </c>
+      <c r="E15" t="n">
+        <v>751.61</v>
+      </c>
+      <c r="F15" t="n">
+        <v>574.55</v>
+      </c>
+      <c r="G15" t="n">
+        <v>281.65</v>
+      </c>
+      <c r="H15" t="n">
+        <v>210.24</v>
+      </c>
+      <c r="I15" t="n">
+        <v>189.97</v>
+      </c>
+      <c r="J15" t="n">
+        <v>286.46</v>
       </c>
     </row>
   </sheetData>
@@ -13258,11 +13302,11 @@
         <v>210</v>
       </c>
       <c r="C2" t="n">
-        <v>196.19</v>
+        <v>196.56</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -13277,7 +13321,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -13292,7 +13336,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -13306,11 +13350,11 @@
         <v>752</v>
       </c>
       <c r="C5" t="n">
-        <v>750.6900000000001</v>
+        <v>751.13</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -13324,11 +13368,11 @@
         <v>575</v>
       </c>
       <c r="C6" t="n">
-        <v>573.13</v>
+        <v>573.75</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -13342,11 +13386,11 @@
         <v>280</v>
       </c>
       <c r="C7" t="n">
-        <v>278.59</v>
+        <v>278.95</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -13360,11 +13404,11 @@
         <v>221</v>
       </c>
       <c r="C8" t="n">
-        <v>218.42</v>
+        <v>218.46</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -13378,11 +13422,11 @@
         <v>193</v>
       </c>
       <c r="C9" t="n">
-        <v>188</v>
+        <v>188.07</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -13394,7 +13438,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>

--- a/output/Data and Chart Outputs/philippines_dam_levels.xlsx
+++ b/output/Data and Chart Outputs/philippines_dam_levels.xlsx
@@ -157,7 +157,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Angat dam water level (Metro Manila water supply and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-29</a:t>
+              <a:t>Angat dam water level (Metro Manila water supply and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-30</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -428,7 +428,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>San Roque dam water level (hydro, Agno river; PAGASA) - water year (Oct-Sep), data to 2026-10-29</a:t>
+              <a:t>San Roque dam water level (hydro, Agno river; PAGASA) - water year (Oct-Sep), data to 2026-10-30</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -699,7 +699,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Magat dam water level (irrigation and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-29</a:t>
+              <a:t>Magat dam water level (irrigation and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-30</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -970,7 +970,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Pantabangan dam water level (irrigation and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-29</a:t>
+              <a:t>Pantabangan dam water level (irrigation and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-30</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1663,7 +1663,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Daily from 2026-10-02 to 2026-10-29 - PAGASA posts only today's and yesterday's readings, so the history here starts with this pull's first run. Luzon reservoirs: Angat (Metro Manila water supply, 218 MW hydro), Ipo and La Mesa (water supply), Ambuklao, Binga, San Roque (hydro, Agno river), Pantabangan and Magat (irrigation + hydro), Caliraya (pumped storage).</t>
+          <t>Daily from 2026-10-02 to 2026-10-30 - PAGASA posts only today's and yesterday's readings, so the history here starts with this pull's first run. Luzon reservoirs: Angat (Metro Manila water supply, 218 MW hydro), Ipo and La Mesa (water supply), Ambuklao, Binga, San Roque (hydro, Agno river), Pantabangan and Magat (irrigation + hydro), Caliraya (pumped storage).</t>
         </is>
       </c>
     </row>
@@ -2044,6 +2044,9 @@
         <is>
           <t>30-Oct</t>
         </is>
+      </c>
+      <c r="G31" t="n">
+        <v>208.61</v>
       </c>
     </row>
     <row r="32">
@@ -4810,6 +4813,9 @@
           <t>30-Oct</t>
         </is>
       </c>
+      <c r="G31" t="n">
+        <v>281.69</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -7575,6 +7581,9 @@
           <t>30-Oct</t>
         </is>
       </c>
+      <c r="G31" t="n">
+        <v>189.78</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -10340,6 +10349,9 @@
           <t>30-Oct</t>
         </is>
       </c>
+      <c r="G31" t="n">
+        <v>210.27</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -12753,7 +12765,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13254,6 +13266,38 @@
       </c>
       <c r="J15" t="n">
         <v>286.46</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B16" t="n">
+        <v>208.61</v>
+      </c>
+      <c r="C16" t="n">
+        <v>100.59</v>
+      </c>
+      <c r="D16" t="n">
+        <v>79.34999999999999</v>
+      </c>
+      <c r="E16" t="n">
+        <v>751.48</v>
+      </c>
+      <c r="F16" t="n">
+        <v>574.49</v>
+      </c>
+      <c r="G16" t="n">
+        <v>281.69</v>
+      </c>
+      <c r="H16" t="n">
+        <v>210.27</v>
+      </c>
+      <c r="I16" t="n">
+        <v>189.78</v>
+      </c>
+      <c r="J16" t="n">
+        <v>286.28</v>
       </c>
     </row>
   </sheetData>
@@ -13302,11 +13346,11 @@
         <v>210</v>
       </c>
       <c r="C2" t="n">
-        <v>196.56</v>
+        <v>196.93</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -13321,7 +13365,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -13336,7 +13380,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -13350,11 +13394,11 @@
         <v>752</v>
       </c>
       <c r="C5" t="n">
-        <v>751.13</v>
+        <v>751.5599999999999</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -13368,11 +13412,11 @@
         <v>575</v>
       </c>
       <c r="C6" t="n">
-        <v>573.75</v>
+        <v>574.38</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -13386,11 +13430,11 @@
         <v>280</v>
       </c>
       <c r="C7" t="n">
-        <v>278.95</v>
+        <v>279.3</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -13404,11 +13448,11 @@
         <v>221</v>
       </c>
       <c r="C8" t="n">
-        <v>218.46</v>
+        <v>218.5</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -13422,11 +13466,11 @@
         <v>193</v>
       </c>
       <c r="C9" t="n">
-        <v>188.07</v>
+        <v>188.14</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -13438,7 +13482,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>

--- a/output/Data and Chart Outputs/philippines_dam_levels.xlsx
+++ b/output/Data and Chart Outputs/philippines_dam_levels.xlsx
@@ -157,7 +157,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Angat dam water level (Metro Manila water supply and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-30</a:t>
+              <a:t>Angat dam water level (Metro Manila water supply and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-31</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -428,7 +428,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>San Roque dam water level (hydro, Agno river; PAGASA) - water year (Oct-Sep), data to 2026-10-30</a:t>
+              <a:t>San Roque dam water level (hydro, Agno river; PAGASA) - water year (Oct-Sep), data to 2026-10-31</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -699,7 +699,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Magat dam water level (irrigation and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-30</a:t>
+              <a:t>Magat dam water level (irrigation and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-31</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -970,7 +970,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Pantabangan dam water level (irrigation and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-30</a:t>
+              <a:t>Pantabangan dam water level (irrigation and hydro; PAGASA) - water year (Oct-Sep), data to 2026-10-31</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1663,7 +1663,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Daily from 2026-10-02 to 2026-10-30 - PAGASA posts only today's and yesterday's readings, so the history here starts with this pull's first run. Luzon reservoirs: Angat (Metro Manila water supply, 218 MW hydro), Ipo and La Mesa (water supply), Ambuklao, Binga, San Roque (hydro, Agno river), Pantabangan and Magat (irrigation + hydro), Caliraya (pumped storage).</t>
+          <t>Daily from 2026-10-02 to 2026-10-31 - PAGASA posts only today's and yesterday's readings, so the history here starts with this pull's first run. Luzon reservoirs: Angat (Metro Manila water supply, 218 MW hydro), Ipo and La Mesa (water supply), Ambuklao, Binga, San Roque (hydro, Agno river), Pantabangan and Magat (irrigation + hydro), Caliraya (pumped storage).</t>
         </is>
       </c>
     </row>
@@ -2054,6 +2054,9 @@
         <is>
           <t>31-Oct</t>
         </is>
+      </c>
+      <c r="G32" t="n">
+        <v>208.56</v>
       </c>
     </row>
     <row r="33">
@@ -4823,6 +4826,9 @@
           <t>31-Oct</t>
         </is>
       </c>
+      <c r="G32" t="n">
+        <v>281.7</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -7591,6 +7597,9 @@
           <t>31-Oct</t>
         </is>
       </c>
+      <c r="G32" t="n">
+        <v>189.62</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -10359,6 +10368,9 @@
           <t>31-Oct</t>
         </is>
       </c>
+      <c r="G32" t="n">
+        <v>210.29</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -12765,7 +12777,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13298,6 +13310,38 @@
       </c>
       <c r="J16" t="n">
         <v>286.28</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="B17" t="n">
+        <v>208.56</v>
+      </c>
+      <c r="C17" t="n">
+        <v>100.84</v>
+      </c>
+      <c r="D17" t="n">
+        <v>79.38</v>
+      </c>
+      <c r="E17" t="n">
+        <v>751.35</v>
+      </c>
+      <c r="F17" t="n">
+        <v>574.6</v>
+      </c>
+      <c r="G17" t="n">
+        <v>281.7</v>
+      </c>
+      <c r="H17" t="n">
+        <v>210.29</v>
+      </c>
+      <c r="I17" t="n">
+        <v>189.62</v>
+      </c>
+      <c r="J17" t="n">
+        <v>286.2</v>
       </c>
     </row>
   </sheetData>
@@ -13346,11 +13390,11 @@
         <v>210</v>
       </c>
       <c r="C2" t="n">
-        <v>196.93</v>
+        <v>197.3</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
@@ -13365,7 +13409,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
@@ -13380,7 +13424,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
@@ -13394,11 +13438,11 @@
         <v>752</v>
       </c>
       <c r="C5" t="n">
-        <v>751.5599999999999</v>
+        <v>752</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
@@ -13412,11 +13456,11 @@
         <v>575</v>
       </c>
       <c r="C6" t="n">
-        <v>574.38</v>
+        <v>575</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
@@ -13430,11 +13474,11 @@
         <v>280</v>
       </c>
       <c r="C7" t="n">
-        <v>279.3</v>
+        <v>279.65</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
@@ -13448,11 +13492,11 @@
         <v>221</v>
       </c>
       <c r="C8" t="n">
-        <v>218.5</v>
+        <v>218.54</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
@@ -13466,11 +13510,11 @@
         <v>193</v>
       </c>
       <c r="C9" t="n">
-        <v>188.14</v>
+        <v>188.21</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
@@ -13482,7 +13526,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
